--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,15 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StationID</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Original_Cluster</t>
@@ -473,7 +468,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -481,37 +476,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,19 +516,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -545,55 +540,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -623,22 +618,22 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -653,22 +648,22 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -683,37 +678,37 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -721,74 +716,74 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -803,15 +798,15 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -821,49 +816,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -871,7 +866,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -881,53 +876,53 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -938,26 +933,26 @@
         <v>3</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -965,85 +960,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1051,7 +1046,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1061,34 +1056,34 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1111,29 +1106,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1141,33 +1136,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1175,25 +1170,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1201,33 +1196,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1235,25 +1230,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1261,20 +1256,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1283,37 +1278,37 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1316,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1331,53 +1326,53 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1385,29 +1380,29 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1415,25 +1410,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1451,19 +1446,19 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1471,33 +1466,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1505,25 +1500,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1531,59 +1526,59 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1591,29 +1586,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1631,49 +1626,49 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1685,29 +1680,29 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1718,256 +1713,16 @@
         <v>3</v>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,20 +476,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -510,46 +510,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -558,11 +558,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -588,28 +588,28 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -626,20 +626,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -648,28 +648,28 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -678,7 +678,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -686,29 +686,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -729,16 +729,16 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -746,50 +746,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -798,11 +798,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -846,19 +846,19 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -866,33 +866,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
@@ -918,7 +918,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -926,33 +926,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -960,37 +960,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -999,37 +999,37 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1056,40 +1056,40 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1098,28 +1098,28 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1136,29 +1136,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1170,16 +1170,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1206,23 +1206,23 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1230,29 +1230,29 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1278,11 +1278,11 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1290,25 +1290,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1326,53 +1326,53 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1380,59 +1380,59 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1488,37 +1488,37 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1526,33 +1526,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1560,29 +1560,29 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1593,22 +1593,22 @@
         <v>1</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1629,20 +1629,20 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1650,46 +1650,46 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1698,31 +1698,541 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,6 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>MRT_Cluster 2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>MRT_Cluster 3</t>
         </is>
       </c>
@@ -476,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,13 +481,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +498,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -520,9 +512,6 @@
       </c>
       <c r="G3" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +521,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -550,9 +539,6 @@
       </c>
       <c r="G4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -581,9 +567,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -606,13 +589,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -622,26 +602,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -666,13 +643,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -686,7 +660,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -696,12 +670,9 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -712,26 +683,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -746,7 +714,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -759,9 +727,6 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -791,18 +756,15 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -816,49 +778,43 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -866,7 +822,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -879,80 +835,71 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H16" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -963,52 +910,46 @@
         <v>1</v>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1016,7 +957,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1029,16 +970,13 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1046,7 +984,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1059,16 +997,13 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1076,7 +1011,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1090,15 +1025,12 @@
       </c>
       <c r="G22" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1119,16 +1051,13 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1136,7 +1065,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1149,16 +1078,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1166,7 +1092,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1179,16 +1105,13 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1209,76 +1132,67 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1299,16 +1213,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1329,16 +1240,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1359,46 +1267,40 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1406,7 +1308,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1419,16 +1321,13 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1449,16 +1348,13 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1362,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1479,46 +1375,40 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1526,7 +1416,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1539,46 +1429,40 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1586,7 +1470,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1599,16 +1483,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1616,7 +1497,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1626,79 +1507,70 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1706,7 +1578,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1719,16 +1591,13 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1736,7 +1605,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1746,19 +1615,16 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1766,89 +1632,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1856,7 +1713,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1870,15 +1727,12 @@
       </c>
       <c r="G48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1886,7 +1740,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1896,19 +1750,16 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1916,33 +1767,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H50" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1953,22 +1801,19 @@
         <v>1</v>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1976,7 +1821,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1989,16 +1834,13 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2006,7 +1848,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2016,223 +1858,10 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="b">
-        <v>1</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,11 +521,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -602,18 +602,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -683,18 +683,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -760,11 +760,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -778,43 +778,43 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -841,65 +841,65 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -910,46 +910,46 @@
         <v>1</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -976,7 +976,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1003,7 +1003,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1021,16 +1021,16 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1057,7 +1057,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1084,7 +1084,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1111,7 +1111,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1138,22 +1138,22 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -1165,22 +1165,22 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1192,7 +1192,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1219,7 +1219,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1246,7 +1246,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1273,34 +1273,34 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1327,7 +1327,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1354,7 +1354,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1381,22 +1381,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -1408,7 +1408,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1435,22 +1435,22 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -1462,7 +1462,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1489,7 +1489,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1516,22 +1516,22 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -1543,22 +1543,22 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -1570,7 +1570,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1597,7 +1597,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1624,7 +1624,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1651,22 +1651,22 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -1678,22 +1678,22 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -1705,7 +1705,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1723,16 +1723,16 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1759,7 +1759,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1777,31 +1777,31 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1840,27 +1840,216 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
         <v>0.5</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G60" t="n">
         <v>0.5</v>
       </c>
     </row>
